--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_10/epoch_140/per_file_predictions_epoch_140.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_10/epoch_140/per_file_predictions_epoch_140.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9097,0.0426,0.0097,0.0062</t>
-  </si>
-  <si>
-    <t>0.9047,0.0335,0.0193,0.0164</t>
-  </si>
-  <si>
-    <t>0.9779,0.0091,0.0056,0.0009</t>
-  </si>
-  <si>
-    <t>0.9770,0.0047,0.0058,0.0025</t>
-  </si>
-  <si>
-    <t>0.9570,0.0140,0.0018,0.0048</t>
-  </si>
-  <si>
-    <t>0.8718,0.0682,0.0061,0.0082</t>
-  </si>
-  <si>
-    <t>0.9156,0.0858,0.0031,0.0009</t>
-  </si>
-  <si>
-    <t>0.9382,0.0290,0.0037,0.0038</t>
-  </si>
-  <si>
-    <t>0.9194,0.0546,0.0034,0.0034</t>
-  </si>
-  <si>
-    <t>0.8795,0.0872,0.0035,0.0029</t>
-  </si>
-  <si>
-    <t>0.9499,0.0330,0.0022,0.0024</t>
-  </si>
-  <si>
-    <t>0.8950,0.0385,0.0034,0.0076</t>
-  </si>
-  <si>
-    <t>0.9935,0.0017,0.0015,0.0002</t>
-  </si>
-  <si>
-    <t>0.9810,0.0105,0.0026,0.0002</t>
-  </si>
-  <si>
-    <t>0.9921,0.0016,0.0037,0.0002</t>
-  </si>
-  <si>
-    <t>0.9880,0.0027,0.0069,0.0002</t>
-  </si>
-  <si>
-    <t>0.9916,0.0024,0.0014,0.0003</t>
-  </si>
-  <si>
-    <t>0.9547,0.0508,0.0039,0.0003</t>
-  </si>
-  <si>
-    <t>0.6172,0.5325,0.0070,0.0003</t>
-  </si>
-  <si>
-    <t>0.8033,0.2699,0.0073,0.0006</t>
-  </si>
-  <si>
-    <t>0.8964,0.1325,0.0087,0.0008</t>
-  </si>
-  <si>
-    <t>0.3712,0.7572,0.0015,0.0004</t>
-  </si>
-  <si>
-    <t>0.9738,0.0034,0.0316,0.0011</t>
-  </si>
-  <si>
-    <t>0.9821,0.0050,0.0085,0.0010</t>
-  </si>
-  <si>
-    <t>0.9752,0.0050,0.0198,0.0007</t>
-  </si>
-  <si>
-    <t>0.9745,0.0076,0.0194,0.0005</t>
-  </si>
-  <si>
-    <t>0.9892,0.0016,0.0074,0.0006</t>
-  </si>
-  <si>
-    <t>0.9479,0.0237,0.0169,0.0006</t>
-  </si>
-  <si>
-    <t>0.9457,0.0080,0.0764,0.0006</t>
-  </si>
-  <si>
-    <t>0.8192,0.2159,0.0133,0.0015</t>
-  </si>
-  <si>
-    <t>0.9887,0.0047,0.0023,0.0004</t>
-  </si>
-  <si>
-    <t>0.7895,0.1244,0.1198,0.0050</t>
-  </si>
-  <si>
-    <t>0.9102,0.1085,0.0085,0.0003</t>
-  </si>
-  <si>
-    <t>0.9564,0.0332,0.0070,0.0013</t>
-  </si>
-  <si>
-    <t>0.9810,0.0105,0.0031,0.0008</t>
-  </si>
-  <si>
-    <t>0.8654,0.1390,0.0019,0.0017</t>
-  </si>
-  <si>
-    <t>0.9521,0.0295,0.0131,0.0022</t>
-  </si>
-  <si>
-    <t>0.7063,0.2690,0.0759,0.0013</t>
-  </si>
-  <si>
-    <t>0.9755,0.0024,0.0398,0.0010</t>
-  </si>
-  <si>
-    <t>0.9735,0.0066,0.0212,0.0016</t>
-  </si>
-  <si>
-    <t>0.9742,0.0021,0.0251,0.0024</t>
-  </si>
-  <si>
-    <t>0.6900,0.2166,0.1168,0.0012</t>
-  </si>
-  <si>
-    <t>0.2986,0.6767,0.1254,0.0019</t>
-  </si>
-  <si>
-    <t>0.9177,0.0332,0.0462,0.0006</t>
-  </si>
-  <si>
-    <t>0.9683,0.0140,0.0050,0.0017</t>
-  </si>
-  <si>
-    <t>0.8798,0.1737,0.0020,0.0003</t>
-  </si>
-  <si>
-    <t>0.8529,0.2071,0.0061,0.0002</t>
-  </si>
-  <si>
-    <t>0.6615,0.3789,0.0186,0.0017</t>
-  </si>
-  <si>
-    <t>0.6563,0.0578,0.4337,0.0061</t>
-  </si>
-  <si>
-    <t>0.8457,0.0750,0.0907,0.0028</t>
-  </si>
-  <si>
-    <t>0.9754,0.0048,0.0229,0.0006</t>
-  </si>
-  <si>
-    <t>0.8675,0.0922,0.0263,0.0020</t>
-  </si>
-  <si>
-    <t>0.6263,0.1022,0.2977,0.0022</t>
-  </si>
-  <si>
-    <t>0.8328,0.0596,0.1083,0.0012</t>
-  </si>
-  <si>
-    <t>0.4529,0.4959,0.0218,0.0161</t>
-  </si>
-  <si>
-    <t>0.9567,0.0345,0.0028,0.0017</t>
-  </si>
-  <si>
-    <t>0.8228,0.1267,0.0041,0.0054</t>
-  </si>
-  <si>
-    <t>0.5156,0.5718,0.0600,0.0029</t>
-  </si>
-  <si>
-    <t>0.8709,0.0835,0.0121,0.0070</t>
-  </si>
-  <si>
-    <t>0.8507,0.1038,0.0135,0.0112</t>
-  </si>
-  <si>
-    <t>0.9267,0.0502,0.0038,0.0030</t>
-  </si>
-  <si>
-    <t>0.0452,0.7849,0.7425,0.0020</t>
-  </si>
-  <si>
-    <t>0.8167,0.0137,0.3824,0.0008</t>
-  </si>
-  <si>
-    <t>0.9481,0.0055,0.1006,0.0008</t>
-  </si>
-  <si>
-    <t>0.0042,0.9681,0.8627,0.0016</t>
-  </si>
-  <si>
-    <t>0.8191,0.0163,0.2875,0.0012</t>
-  </si>
-  <si>
-    <t>0.9265,0.1666,0.0010,0.0000</t>
-  </si>
-  <si>
-    <t>0.1091,0.9521,0.0013,0.0001</t>
-  </si>
-  <si>
-    <t>0.9312,0.0706,0.0117,0.0008</t>
-  </si>
-  <si>
-    <t>0.9773,0.0153,0.0024,0.0006</t>
-  </si>
-  <si>
-    <t>0.0856,0.7356,0.4341,0.0110</t>
-  </si>
-  <si>
-    <t>0.3347,0.4059,0.3975,0.0052</t>
-  </si>
-  <si>
-    <t>0.5741,0.3468,0.0941,0.0008</t>
-  </si>
-  <si>
-    <t>0.0613,0.8978,0.3236,0.0026</t>
-  </si>
-  <si>
-    <t>0.1456,0.8832,0.0574,0.0001</t>
-  </si>
-  <si>
-    <t>0.9738,0.0047,0.0192,0.0022</t>
-  </si>
-  <si>
-    <t>0.9439,0.0251,0.0200,0.0031</t>
-  </si>
-  <si>
-    <t>0.9039,0.0082,0.0108,0.0527</t>
-  </si>
-  <si>
-    <t>0.9623,0.0073,0.0064,0.0090</t>
-  </si>
-  <si>
-    <t>0.9630,0.0032,0.0216,0.0072</t>
-  </si>
-  <si>
-    <t>0.9346,0.0310,0.0096,0.0041</t>
-  </si>
-  <si>
-    <t>0.0153,0.9251,0.6936,0.0008</t>
-  </si>
-  <si>
-    <t>0.3139,0.4173,0.3997,0.0027</t>
-  </si>
-  <si>
-    <t>0.7937,0.0546,0.2115,0.0069</t>
-  </si>
-  <si>
-    <t>0.9064,0.0318,0.0553,0.0016</t>
-  </si>
-  <si>
-    <t>0.5151,0.2883,0.2164,0.0009</t>
-  </si>
-  <si>
-    <t>0.2144,0.5650,0.4188,0.0030</t>
-  </si>
-  <si>
-    <t>0.9573,0.0399,0.0021,0.0008</t>
-  </si>
-  <si>
-    <t>0.9122,0.0682,0.0147,0.0046</t>
-  </si>
-  <si>
-    <t>0.8520,0.0767,0.0095,0.0127</t>
-  </si>
-  <si>
-    <t>0.8615,0.0685,0.0102,0.0212</t>
-  </si>
-  <si>
-    <t>0.8883,0.0574,0.0155,0.0123</t>
-  </si>
-  <si>
-    <t>0.8965,0.0524,0.0136,0.0128</t>
-  </si>
-  <si>
-    <t>0.8529,0.0957,0.0120,0.0109</t>
-  </si>
-  <si>
-    <t>0.8973,0.0504,0.0082,0.0090</t>
-  </si>
-  <si>
-    <t>0.9238,0.0447,0.0046,0.0069</t>
-  </si>
-  <si>
-    <t>0.9273,0.0337,0.0031,0.0057</t>
-  </si>
-  <si>
-    <t>0.6938,0.0866,0.0085,0.0669</t>
-  </si>
-  <si>
-    <t>0.9759,0.0165,0.0021,0.0011</t>
-  </si>
-  <si>
-    <t>0.8978,0.0678,0.0041,0.0023</t>
-  </si>
-  <si>
-    <t>0.8288,0.1059,0.0110,0.0097</t>
-  </si>
-  <si>
-    <t>0.9515,0.0349,0.0017,0.0014</t>
-  </si>
-  <si>
-    <t>0.8842,0.0609,0.0081,0.0110</t>
-  </si>
-  <si>
-    <t>0.3607,0.0759,0.7180,0.0028</t>
-  </si>
-  <si>
-    <t>0.9868,0.0033,0.0077,0.0002</t>
-  </si>
-  <si>
-    <t>0.9909,0.0017,0.0051,0.0003</t>
-  </si>
-  <si>
-    <t>0.9905,0.0013,0.0133,0.0002</t>
-  </si>
-  <si>
-    <t>0.0454,0.9640,0.0075,0.0018</t>
-  </si>
-  <si>
-    <t>0.0710,0.9434,0.0035,0.0010</t>
-  </si>
-  <si>
-    <t>0.7616,0.2900,0.0037,0.0010</t>
-  </si>
-  <si>
-    <t>0.3169,0.7685,0.0046,0.0008</t>
-  </si>
-  <si>
-    <t>0.0408,0.9573,0.0092,0.0054</t>
-  </si>
-  <si>
-    <t>0.3225,0.7246,0.0116,0.0033</t>
-  </si>
-  <si>
-    <t>0.9772,0.0107,0.0039,0.0011</t>
-  </si>
-  <si>
-    <t>0.9930,0.0020,0.0030,0.0001</t>
-  </si>
-  <si>
-    <t>0.9855,0.0026,0.0101,0.0003</t>
-  </si>
-  <si>
-    <t>0.9686,0.0074,0.0194,0.0009</t>
-  </si>
-  <si>
-    <t>0.9366,0.0577,0.0118,0.0003</t>
-  </si>
-  <si>
-    <t>0.9389,0.0310,0.0151,0.0023</t>
-  </si>
-  <si>
-    <t>0.6328,0.4950,0.0037,0.0005</t>
-  </si>
-  <si>
-    <t>0.9403,0.0518,0.0063,0.0005</t>
-  </si>
-  <si>
-    <t>0.8726,0.1539,0.0099,0.0006</t>
-  </si>
-  <si>
-    <t>0.4918,0.4306,0.1036,0.0009</t>
-  </si>
-  <si>
-    <t>0.9752,0.0236,0.0011,0.0003</t>
-  </si>
-  <si>
-    <t>0.8328,0.1632,0.0024,0.0026</t>
-  </si>
-  <si>
-    <t>0.9036,0.0995,0.0027,0.0012</t>
-  </si>
-  <si>
-    <t>0.9237,0.0564,0.0193,0.0040</t>
-  </si>
-  <si>
-    <t>0.9704,0.0148,0.0019,0.0028</t>
-  </si>
-  <si>
-    <t>0.9034,0.0788,0.0060,0.0038</t>
-  </si>
-  <si>
-    <t>0.9531,0.0272,0.0128,0.0035</t>
-  </si>
-  <si>
-    <t>0.9621,0.0250,0.0024,0.0020</t>
-  </si>
-  <si>
-    <t>0.9495,0.0594,0.0039,0.0004</t>
-  </si>
-  <si>
-    <t>0.7124,0.2410,0.0273,0.0065</t>
-  </si>
-  <si>
-    <t>0.9332,0.0414,0.0044,0.0044</t>
-  </si>
-  <si>
-    <t>0.3772,0.4999,0.2825,0.0297</t>
-  </si>
-  <si>
-    <t>0.6093,0.3592,0.0637,0.0022</t>
-  </si>
-  <si>
-    <t>0.8140,0.0377,0.1994,0.0033</t>
-  </si>
-  <si>
-    <t>0.8996,0.0709,0.0303,0.0004</t>
-  </si>
-  <si>
-    <t>0.9645,0.0094,0.0260,0.0010</t>
-  </si>
-  <si>
-    <t>0.9934,0.0018,0.0016,0.0002</t>
-  </si>
-  <si>
-    <t>0.9749,0.0052,0.0214,0.0013</t>
-  </si>
-  <si>
-    <t>0.9701,0.0159,0.0087,0.0005</t>
-  </si>
-  <si>
-    <t>0.9421,0.0141,0.0154,0.0105</t>
-  </si>
-  <si>
-    <t>0.9163,0.0050,0.0146,0.0376</t>
-  </si>
-  <si>
-    <t>0.9636,0.0040,0.0056,0.0135</t>
-  </si>
-  <si>
-    <t>0.9535,0.0132,0.0226,0.0073</t>
-  </si>
-  <si>
-    <t>0.4436,0.4658,0.1901,0.0061</t>
-  </si>
-  <si>
-    <t>0.6862,0.2601,0.0462,0.0276</t>
-  </si>
-  <si>
-    <t>0.8601,0.1095,0.0449,0.0076</t>
-  </si>
-  <si>
-    <t>0.8812,0.1188,0.0079,0.0023</t>
-  </si>
-  <si>
-    <t>0.8956,0.0801,0.0202,0.0032</t>
-  </si>
-  <si>
-    <t>0.9764,0.0095,0.0044,0.0015</t>
-  </si>
-  <si>
-    <t>0.9600,0.0188,0.0050,0.0017</t>
-  </si>
-  <si>
-    <t>0.9314,0.0483,0.0108,0.0045</t>
-  </si>
-  <si>
-    <t>0.1492,0.4428,0.7204,0.0531</t>
-  </si>
-  <si>
-    <t>0.9353,0.0496,0.0016,0.0006</t>
-  </si>
-  <si>
-    <t>0.8883,0.0839,0.0061,0.0034</t>
-  </si>
-  <si>
-    <t>0.9136,0.0744,0.0127,0.0011</t>
-  </si>
-  <si>
-    <t>0.9565,0.0169,0.0033,0.0039</t>
-  </si>
-  <si>
-    <t>0.9920,0.0061,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.9381,0.0539,0.0081,0.0006</t>
-  </si>
-  <si>
-    <t>0.7372,0.2781,0.0119,0.0009</t>
-  </si>
-  <si>
-    <t>0.9859,0.0062,0.0038,0.0004</t>
-  </si>
-  <si>
-    <t>0.8268,0.1244,0.0064,0.0053</t>
-  </si>
-  <si>
-    <t>0.8713,0.0835,0.0055,0.0084</t>
-  </si>
-  <si>
-    <t>0.9302,0.0378,0.0080,0.0085</t>
-  </si>
-  <si>
-    <t>0.9645,0.0220,0.0061,0.0026</t>
-  </si>
-  <si>
-    <t>0.9085,0.0539,0.0101,0.0065</t>
-  </si>
-  <si>
-    <t>0.8756,0.0655,0.0117,0.0101</t>
-  </si>
-  <si>
-    <t>0.8985,0.0658,0.0118,0.0073</t>
-  </si>
-  <si>
-    <t>0.8516,0.0657,0.0112,0.0186</t>
-  </si>
-  <si>
-    <t>0.9278,0.0713,0.0142,0.0014</t>
-  </si>
-  <si>
-    <t>0.5712,0.4321,0.0239,0.0095</t>
-  </si>
-  <si>
-    <t>0.5655,0.4069,0.0050,0.0056</t>
-  </si>
-  <si>
-    <t>0.8513,0.1638,0.0044,0.0012</t>
-  </si>
-  <si>
-    <t>0.8354,0.2095,0.0039,0.0010</t>
-  </si>
-  <si>
-    <t>0.9140,0.0795,0.0061,0.0023</t>
-  </si>
-  <si>
-    <t>0.6005,0.4992,0.0029,0.0013</t>
-  </si>
-  <si>
-    <t>0.5325,0.5530,0.0130,0.0014</t>
-  </si>
-  <si>
-    <t>0.0224,0.4830,0.8121,0.0023</t>
-  </si>
-  <si>
-    <t>0.9880,0.0064,0.0013,0.0007</t>
-  </si>
-  <si>
-    <t>0.8778,0.0898,0.0253,0.0012</t>
-  </si>
-  <si>
-    <t>0.9556,0.0185,0.0170,0.0006</t>
-  </si>
-  <si>
-    <t>0.9452,0.0201,0.0214,0.0007</t>
-  </si>
-  <si>
-    <t>0.1620,0.3350,0.7372,0.0005</t>
-  </si>
-  <si>
-    <t>0.9706,0.0107,0.0167,0.0004</t>
-  </si>
-  <si>
-    <t>0.9792,0.0050,0.0175,0.0001</t>
-  </si>
-  <si>
-    <t>0.4718,0.1800,0.4044,0.0042</t>
-  </si>
-  <si>
-    <t>0.9349,0.0316,0.0152,0.0015</t>
-  </si>
-  <si>
-    <t>0.9881,0.0036,0.0061,0.0002</t>
-  </si>
-  <si>
-    <t>0.9621,0.0324,0.0060,0.0002</t>
-  </si>
-  <si>
-    <t>0.9944,0.0018,0.0013,0.0002</t>
-  </si>
-  <si>
-    <t>0.9742,0.0180,0.0063,0.0001</t>
-  </si>
-  <si>
-    <t>0.9327,0.0281,0.0134,0.0030</t>
-  </si>
-  <si>
-    <t>0.9953,0.0014,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.9857,0.0069,0.0026,0.0002</t>
-  </si>
-  <si>
-    <t>0.9447,0.0593,0.0030,0.0008</t>
-  </si>
-  <si>
-    <t>0.8995,0.1338,0.0013,0.0007</t>
-  </si>
-  <si>
-    <t>0.9710,0.0267,0.0020,0.0007</t>
-  </si>
-  <si>
-    <t>0.8861,0.0961,0.0142,0.0055</t>
-  </si>
-  <si>
-    <t>0.9162,0.0499,0.0041,0.0049</t>
-  </si>
-  <si>
-    <t>0.9937,0.0026,0.0018,0.0001</t>
-  </si>
-  <si>
-    <t>0.9879,0.0030,0.0066,0.0007</t>
-  </si>
-  <si>
-    <t>0.9853,0.0037,0.0079,0.0004</t>
-  </si>
-  <si>
-    <t>0.9945,0.0011,0.0047,0.0000</t>
-  </si>
-  <si>
-    <t>0.9609,0.0098,0.0308,0.0020</t>
-  </si>
-  <si>
-    <t>0.7980,0.0331,0.2007,0.0014</t>
-  </si>
-  <si>
-    <t>0.8891,0.0505,0.0415,0.0012</t>
-  </si>
-  <si>
-    <t>0.8954,0.0433,0.0700,0.0023</t>
-  </si>
-  <si>
-    <t>0.7855,0.0937,0.1428,0.0021</t>
-  </si>
-  <si>
-    <t>0.4767,0.1722,0.4237,0.0026</t>
-  </si>
-  <si>
-    <t>0.7847,0.1112,0.0085,0.0176</t>
-  </si>
-  <si>
-    <t>0.8171,0.1614,0.0221,0.0074</t>
-  </si>
-  <si>
-    <t>0.8641,0.1169,0.0096,0.0046</t>
-  </si>
-  <si>
-    <t>0.9397,0.0352,0.0043,0.0040</t>
-  </si>
-  <si>
-    <t>0.8880,0.0849,0.0074,0.0036</t>
-  </si>
-  <si>
-    <t>0.8363,0.0980,0.0137,0.0080</t>
-  </si>
-  <si>
-    <t>0.8712,0.0710,0.0066,0.0070</t>
-  </si>
-  <si>
-    <t>0.9489,0.0334,0.0049,0.0024</t>
-  </si>
-  <si>
-    <t>0.9176,0.0333,0.0525,0.0044</t>
-  </si>
-  <si>
-    <t>0.9514,0.0429,0.0032,0.0008</t>
-  </si>
-  <si>
-    <t>0.9797,0.0124,0.0026,0.0006</t>
-  </si>
-  <si>
-    <t>0.9439,0.0120,0.0699,0.0006</t>
-  </si>
-  <si>
-    <t>0.5302,0.0947,0.4763,0.0058</t>
-  </si>
-  <si>
-    <t>0.9110,0.0188,0.0850,0.0010</t>
-  </si>
-  <si>
-    <t>0.7913,0.0197,0.2751,0.0006</t>
-  </si>
-  <si>
-    <t>0.9800,0.0057,0.0124,0.0009</t>
-  </si>
-  <si>
-    <t>0.7045,0.0168,0.4629,0.0042</t>
-  </si>
-  <si>
-    <t>0.7106,0.1730,0.1554,0.0040</t>
-  </si>
-  <si>
-    <t>0.9464,0.0301,0.0156,0.0006</t>
-  </si>
-  <si>
-    <t>0.9744,0.0076,0.0128,0.0005</t>
-  </si>
-  <si>
-    <t>0.9873,0.0022,0.0048,0.0011</t>
-  </si>
-  <si>
-    <t>0.9820,0.0076,0.0055,0.0002</t>
-  </si>
-  <si>
-    <t>0.9143,0.0639,0.0087,0.0054</t>
-  </si>
-  <si>
-    <t>0.8911,0.0808,0.0072,0.0036</t>
-  </si>
-  <si>
-    <t>0.8817,0.0854,0.0082,0.0048</t>
-  </si>
-  <si>
-    <t>0.7654,0.1629,0.0143,0.0120</t>
-  </si>
-  <si>
-    <t>0.7838,0.1644,0.0107,0.0090</t>
-  </si>
-  <si>
-    <t>0.8642,0.0752,0.0126,0.0125</t>
-  </si>
-  <si>
-    <t>0.8978,0.0641,0.0059,0.0064</t>
-  </si>
-  <si>
-    <t>0.8721,0.1237,0.0063,0.0036</t>
-  </si>
-  <si>
-    <t>0.9846,0.0053,0.0096,0.0002</t>
-  </si>
-  <si>
-    <t>0.7294,0.1380,0.1426,0.0023</t>
-  </si>
-  <si>
-    <t>0.2568,0.2683,0.5724,0.0036</t>
-  </si>
-  <si>
-    <t>0.9809,0.0072,0.0085,0.0003</t>
-  </si>
-  <si>
-    <t>0.8089,0.0202,0.3275,0.0014</t>
-  </si>
-  <si>
-    <t>0.9782,0.0023,0.0133,0.0026</t>
-  </si>
-  <si>
-    <t>0.9844,0.0039,0.0111,0.0004</t>
-  </si>
-  <si>
-    <t>0.7272,0.1151,0.1887,0.0050</t>
-  </si>
-  <si>
-    <t>0.9727,0.0053,0.0070,0.0038</t>
-  </si>
-  <si>
-    <t>0.9832,0.0019,0.0044,0.0027</t>
-  </si>
-  <si>
-    <t>0.9658,0.0056,0.0059,0.0097</t>
-  </si>
-  <si>
-    <t>0.9783,0.0019,0.0081,0.0038</t>
-  </si>
-  <si>
-    <t>0.9794,0.0013,0.0099,0.0044</t>
-  </si>
-  <si>
-    <t>0.9713,0.0114,0.0066,0.0018</t>
+    <t>0.7084,0.1055,0.0054,0.2131</t>
+  </si>
+  <si>
+    <t>0.0292,0.0007,0.0007,0.9908</t>
+  </si>
+  <si>
+    <t>0.8895,0.0050,0.0033,0.1164</t>
+  </si>
+  <si>
+    <t>0.0161,0.0007,0.0011,0.9921</t>
+  </si>
+  <si>
+    <t>0.9987,0.0003,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9976,0.0007,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9969,0.0001,0.0000,0.0022</t>
+  </si>
+  <si>
+    <t>0.9988,0.0000,0.0000,0.0007</t>
+  </si>
+  <si>
+    <t>0.9914,0.0022,0.0005,0.0031</t>
+  </si>
+  <si>
+    <t>0.9941,0.0021,0.0005,0.0016</t>
+  </si>
+  <si>
+    <t>0.9939,0.0016,0.0004,0.0021</t>
+  </si>
+  <si>
+    <t>0.9867,0.0028,0.0005,0.0048</t>
+  </si>
+  <si>
+    <t>0.8797,0.0087,0.1646,0.0037</t>
+  </si>
+  <si>
+    <t>0.0210,0.0053,0.9725,0.0025</t>
+  </si>
+  <si>
+    <t>0.4054,0.0083,0.7341,0.0013</t>
+  </si>
+  <si>
+    <t>0.0752,0.0485,0.9069,0.0020</t>
+  </si>
+  <si>
+    <t>0.9559,0.0094,0.0281,0.0040</t>
+  </si>
+  <si>
+    <t>0.0052,0.9938,0.0014,0.0005</t>
+  </si>
+  <si>
+    <t>0.0849,0.9174,0.0078,0.0051</t>
+  </si>
+  <si>
+    <t>0.0982,0.9352,0.0011,0.0011</t>
+  </si>
+  <si>
+    <t>0.0179,0.9824,0.0022,0.0009</t>
+  </si>
+  <si>
+    <t>0.0016,0.9967,0.0009,0.0008</t>
+  </si>
+  <si>
+    <t>0.9562,0.0011,0.0480,0.0042</t>
+  </si>
+  <si>
+    <t>0.2047,0.0132,0.8219,0.0041</t>
+  </si>
+  <si>
+    <t>0.0044,0.0120,0.9797,0.0183</t>
+  </si>
+  <si>
+    <t>0.2188,0.0297,0.7721,0.0148</t>
+  </si>
+  <si>
+    <t>0.0257,0.0375,0.9390,0.0050</t>
+  </si>
+  <si>
+    <t>0.0557,0.0073,0.9249,0.0193</t>
+  </si>
+  <si>
+    <t>0.1119,0.0113,0.9015,0.0211</t>
+  </si>
+  <si>
+    <t>0.0498,0.9505,0.0114,0.0026</t>
+  </si>
+  <si>
+    <t>0.7730,0.1075,0.1400,0.0234</t>
+  </si>
+  <si>
+    <t>0.0018,0.0040,0.9937,0.0050</t>
+  </si>
+  <si>
+    <t>0.0073,0.9605,0.0244,0.0053</t>
+  </si>
+  <si>
+    <t>0.9630,0.0376,0.0042,0.0028</t>
+  </si>
+  <si>
+    <t>0.8916,0.0153,0.0795,0.0117</t>
+  </si>
+  <si>
+    <t>0.6020,0.5782,0.0054,0.0011</t>
+  </si>
+  <si>
+    <t>0.0058,0.9807,0.2302,0.0011</t>
+  </si>
+  <si>
+    <t>0.0229,0.8976,0.0539,0.0387</t>
+  </si>
+  <si>
+    <t>0.0512,0.0103,0.9464,0.0054</t>
+  </si>
+  <si>
+    <t>0.1729,0.0084,0.8708,0.0030</t>
+  </si>
+  <si>
+    <t>0.5233,0.0122,0.3928,0.1022</t>
+  </si>
+  <si>
+    <t>0.0089,0.0151,0.9840,0.0018</t>
+  </si>
+  <si>
+    <t>0.0032,0.9742,0.0173,0.0021</t>
+  </si>
+  <si>
+    <t>0.0089,0.0226,0.9626,0.0074</t>
+  </si>
+  <si>
+    <t>0.3192,0.3785,0.0112,0.3031</t>
+  </si>
+  <si>
+    <t>0.0041,0.9883,0.0040,0.0116</t>
+  </si>
+  <si>
+    <t>0.0050,0.9825,0.0181,0.0031</t>
+  </si>
+  <si>
+    <t>0.0023,0.9907,0.0130,0.0028</t>
+  </si>
+  <si>
+    <t>0.0250,0.0139,0.9712,0.0057</t>
+  </si>
+  <si>
+    <t>0.0075,0.0400,0.9819,0.0052</t>
+  </si>
+  <si>
+    <t>0.0127,0.0012,0.9847,0.0027</t>
+  </si>
+  <si>
+    <t>0.0108,0.0136,0.9798,0.0031</t>
+  </si>
+  <si>
+    <t>0.0088,0.0840,0.9828,0.0011</t>
+  </si>
+  <si>
+    <t>0.0066,0.0400,0.9738,0.0042</t>
+  </si>
+  <si>
+    <t>0.9930,0.0095,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.9842,0.0063,0.0039,0.0040</t>
+  </si>
+  <si>
+    <t>0.9565,0.0443,0.0105,0.0035</t>
+  </si>
+  <si>
+    <t>0.0034,0.0378,0.9916,0.0025</t>
+  </si>
+  <si>
+    <t>0.9947,0.0031,0.0010,0.0009</t>
+  </si>
+  <si>
+    <t>0.9902,0.0088,0.0022,0.0009</t>
+  </si>
+  <si>
+    <t>0.9674,0.0544,0.0024,0.0003</t>
+  </si>
+  <si>
+    <t>0.0005,0.9585,0.9756,0.0002</t>
+  </si>
+  <si>
+    <t>0.0055,0.1470,0.9878,0.0013</t>
+  </si>
+  <si>
+    <t>0.0046,0.0042,0.9890,0.0030</t>
+  </si>
+  <si>
+    <t>0.0002,0.9773,0.9457,0.0001</t>
+  </si>
+  <si>
+    <t>0.0009,0.0039,0.9959,0.0018</t>
+  </si>
+  <si>
+    <t>0.0650,0.9218,0.0418,0.0036</t>
+  </si>
+  <si>
+    <t>0.0352,0.9814,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.7927,0.0806,0.2233,0.0062</t>
+  </si>
+  <si>
+    <t>0.4272,0.0260,0.6671,0.0061</t>
+  </si>
+  <si>
+    <t>0.0035,0.0095,0.9929,0.0023</t>
+  </si>
+  <si>
+    <t>0.0018,0.7165,0.9620,0.0007</t>
+  </si>
+  <si>
+    <t>0.0011,0.6533,0.9832,0.0003</t>
+  </si>
+  <si>
+    <t>0.0005,0.9977,0.0044,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.9845,0.9740,0.0000</t>
+  </si>
+  <si>
+    <t>0.0052,0.0006,0.0576,0.9785</t>
+  </si>
+  <si>
+    <t>0.0036,0.0014,0.0031,0.9963</t>
+  </si>
+  <si>
+    <t>0.0045,0.0030,0.0008,0.9966</t>
+  </si>
+  <si>
+    <t>0.0196,0.0029,0.0020,0.9898</t>
+  </si>
+  <si>
+    <t>0.0006,0.0029,0.0011,0.9987</t>
+  </si>
+  <si>
+    <t>0.0257,0.0022,0.0032,0.9871</t>
+  </si>
+  <si>
+    <t>0.0002,0.9496,0.9685,0.0001</t>
+  </si>
+  <si>
+    <t>0.0014,0.9589,0.8982,0.0011</t>
+  </si>
+  <si>
+    <t>0.0159,0.8587,0.6297,0.0092</t>
+  </si>
+  <si>
+    <t>0.0132,0.5744,0.9151,0.0037</t>
+  </si>
+  <si>
+    <t>0.0112,0.7543,0.7385,0.0012</t>
+  </si>
+  <si>
+    <t>0.0031,0.9514,0.0998,0.0060</t>
+  </si>
+  <si>
+    <t>0.9963,0.0018,0.0008,0.0007</t>
+  </si>
+  <si>
+    <t>0.9912,0.0057,0.0019,0.0009</t>
+  </si>
+  <si>
+    <t>0.9938,0.0029,0.0012,0.0014</t>
+  </si>
+  <si>
+    <t>0.9957,0.0008,0.0002,0.0014</t>
+  </si>
+  <si>
+    <t>0.9971,0.0008,0.0002,0.0008</t>
+  </si>
+  <si>
+    <t>0.9971,0.0011,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9927,0.0028,0.0003,0.0016</t>
+  </si>
+  <si>
+    <t>0.9904,0.0074,0.0035,0.0005</t>
+  </si>
+  <si>
+    <t>0.9974,0.0008,0.0004,0.0006</t>
+  </si>
+  <si>
+    <t>0.9975,0.0007,0.0003,0.0009</t>
+  </si>
+  <si>
+    <t>0.9953,0.0010,0.0007,0.0021</t>
+  </si>
+  <si>
+    <t>0.9983,0.0000,0.0000,0.0014</t>
+  </si>
+  <si>
+    <t>0.9968,0.0015,0.0004,0.0006</t>
+  </si>
+  <si>
+    <t>0.9926,0.0034,0.0014,0.0016</t>
+  </si>
+  <si>
+    <t>0.9985,0.0006,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9980,0.0003,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.0258,0.0020,0.9830,0.0014</t>
+  </si>
+  <si>
+    <t>0.0249,0.0330,0.9570,0.0034</t>
+  </si>
+  <si>
+    <t>0.9074,0.0114,0.0550,0.0231</t>
+  </si>
+  <si>
+    <t>0.0022,0.0025,0.9918,0.0046</t>
+  </si>
+  <si>
+    <t>0.0168,0.9849,0.0007,0.0015</t>
+  </si>
+  <si>
+    <t>0.0714,0.9598,0.0012,0.0004</t>
+  </si>
+  <si>
+    <t>0.0460,0.9481,0.0017,0.0117</t>
+  </si>
+  <si>
+    <t>0.1141,0.9249,0.0016,0.0014</t>
+  </si>
+  <si>
+    <t>0.0985,0.9271,0.0010,0.0023</t>
+  </si>
+  <si>
+    <t>0.0118,0.9833,0.0044,0.0014</t>
+  </si>
+  <si>
+    <t>0.9045,0.1868,0.0013,0.0006</t>
+  </si>
+  <si>
+    <t>0.9494,0.0298,0.0136,0.0034</t>
+  </si>
+  <si>
+    <t>0.0995,0.0284,0.8663,0.0160</t>
+  </si>
+  <si>
+    <t>0.4692,0.3459,0.1336,0.1812</t>
+  </si>
+  <si>
+    <t>0.4809,0.0224,0.5445,0.0195</t>
+  </si>
+  <si>
+    <t>0.2604,0.3009,0.2180,0.5253</t>
+  </si>
+  <si>
+    <t>0.0040,0.9898,0.0088,0.0017</t>
+  </si>
+  <si>
+    <t>0.0069,0.9787,0.0114,0.0073</t>
+  </si>
+  <si>
+    <t>0.0019,0.9910,0.0101,0.0282</t>
+  </si>
+  <si>
+    <t>0.0073,0.7667,0.8670,0.0031</t>
+  </si>
+  <si>
+    <t>0.0186,0.9824,0.0115,0.0001</t>
+  </si>
+  <si>
+    <t>0.3968,0.6943,0.0217,0.0013</t>
+  </si>
+  <si>
+    <t>0.8161,0.3280,0.0034,0.0005</t>
+  </si>
+  <si>
+    <t>0.9736,0.0337,0.0055,0.0014</t>
+  </si>
+  <si>
+    <t>0.9944,0.0017,0.0004,0.0016</t>
+  </si>
+  <si>
+    <t>0.9854,0.0005,0.0002,0.0151</t>
+  </si>
+  <si>
+    <t>0.9755,0.0159,0.0053,0.0054</t>
+  </si>
+  <si>
+    <t>0.9971,0.0003,0.0001,0.0017</t>
+  </si>
+  <si>
+    <t>0.9958,0.0023,0.0016,0.0003</t>
+  </si>
+  <si>
+    <t>0.9954,0.0011,0.0008,0.0013</t>
+  </si>
+  <si>
+    <t>0.9929,0.0017,0.0007,0.0025</t>
+  </si>
+  <si>
+    <t>0.0035,0.1168,0.9713,0.0026</t>
+  </si>
+  <si>
+    <t>0.0027,0.9416,0.3001,0.0004</t>
+  </si>
+  <si>
+    <t>0.0103,0.0721,0.9516,0.0021</t>
+  </si>
+  <si>
+    <t>0.0097,0.0761,0.9761,0.0008</t>
+  </si>
+  <si>
+    <t>0.9803,0.0089,0.0036,0.0023</t>
+  </si>
+  <si>
+    <t>0.9524,0.0036,0.0405,0.0039</t>
+  </si>
+  <si>
+    <t>0.1379,0.0025,0.9192,0.0018</t>
+  </si>
+  <si>
+    <t>0.8803,0.0608,0.0689,0.0122</t>
+  </si>
+  <si>
+    <t>0.1073,0.0008,0.0016,0.9652</t>
+  </si>
+  <si>
+    <t>0.0003,0.0010,0.0005,0.9995</t>
+  </si>
+  <si>
+    <t>0.0010,0.0003,0.0048,0.9981</t>
+  </si>
+  <si>
+    <t>0.0010,0.0004,0.0018,0.9987</t>
+  </si>
+  <si>
+    <t>0.0014,0.7868,0.8079,0.0017</t>
+  </si>
+  <si>
+    <t>0.9954,0.0005,0.0010,0.0015</t>
+  </si>
+  <si>
+    <t>0.5936,0.4803,0.0089,0.0161</t>
+  </si>
+  <si>
+    <t>0.9930,0.0037,0.0008,0.0012</t>
+  </si>
+  <si>
+    <t>0.5521,0.6226,0.0039,0.0009</t>
+  </si>
+  <si>
+    <t>0.9874,0.0005,0.0006,0.0093</t>
+  </si>
+  <si>
+    <t>0.6968,0.0031,0.0051,0.3995</t>
+  </si>
+  <si>
+    <t>0.9743,0.0046,0.0030,0.0183</t>
+  </si>
+  <si>
+    <t>0.0084,0.0066,0.9737,0.0220</t>
+  </si>
+  <si>
+    <t>0.8072,0.0004,0.0007,0.3447</t>
+  </si>
+  <si>
+    <t>0.9622,0.0110,0.0030,0.0157</t>
+  </si>
+  <si>
+    <t>0.8173,0.1575,0.0417,0.0058</t>
+  </si>
+  <si>
+    <t>0.8600,0.0897,0.0099,0.0332</t>
+  </si>
+  <si>
+    <t>0.9790,0.0084,0.0155,0.0019</t>
+  </si>
+  <si>
+    <t>0.7324,0.2222,0.0612,0.0136</t>
+  </si>
+  <si>
+    <t>0.9186,0.0492,0.0381,0.0084</t>
+  </si>
+  <si>
+    <t>0.9895,0.0089,0.0022,0.0006</t>
+  </si>
+  <si>
+    <t>0.9860,0.0012,0.0003,0.0060</t>
+  </si>
+  <si>
+    <t>0.9980,0.0003,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9934,0.0012,0.0007,0.0025</t>
+  </si>
+  <si>
+    <t>0.9935,0.0009,0.0006,0.0029</t>
+  </si>
+  <si>
+    <t>0.9981,0.0003,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9938,0.0026,0.0014,0.0009</t>
+  </si>
+  <si>
+    <t>0.9942,0.0019,0.0004,0.0014</t>
+  </si>
+  <si>
+    <t>0.9981,0.0001,0.0000,0.0011</t>
+  </si>
+  <si>
+    <t>0.9556,0.1145,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.7070,0.4285,0.0068,0.0016</t>
+  </si>
+  <si>
+    <t>0.9485,0.0723,0.0023,0.0021</t>
+  </si>
+  <si>
+    <t>0.0337,0.2124,0.9191,0.0282</t>
+  </si>
+  <si>
+    <t>0.9823,0.0187,0.0021,0.0014</t>
+  </si>
+  <si>
+    <t>0.9854,0.0091,0.0021,0.0023</t>
+  </si>
+  <si>
+    <t>0.9938,0.0029,0.0018,0.0011</t>
+  </si>
+  <si>
+    <t>0.8818,0.1496,0.0020,0.0073</t>
+  </si>
+  <si>
+    <t>0.0020,0.0197,0.9875,0.0056</t>
+  </si>
+  <si>
+    <t>0.9653,0.0207,0.0115,0.0015</t>
+  </si>
+  <si>
+    <t>0.0031,0.0173,0.9902,0.0014</t>
+  </si>
+  <si>
+    <t>0.0409,0.0818,0.9383,0.0041</t>
+  </si>
+  <si>
+    <t>0.0574,0.0016,0.9637,0.0014</t>
+  </si>
+  <si>
+    <t>0.0232,0.0309,0.9737,0.0044</t>
+  </si>
+  <si>
+    <t>0.0004,0.0429,0.9956,0.0007</t>
+  </si>
+  <si>
+    <t>0.0127,0.0084,0.9683,0.0133</t>
+  </si>
+  <si>
+    <t>0.0023,0.0153,0.9906,0.0040</t>
+  </si>
+  <si>
+    <t>0.2318,0.0330,0.7842,0.0080</t>
+  </si>
+  <si>
+    <t>0.0834,0.0167,0.9056,0.0066</t>
+  </si>
+  <si>
+    <t>0.2155,0.0631,0.7318,0.0406</t>
+  </si>
+  <si>
+    <t>0.0720,0.0695,0.8668,0.0053</t>
+  </si>
+  <si>
+    <t>0.2012,0.0974,0.6247,0.0015</t>
+  </si>
+  <si>
+    <t>0.3149,0.0931,0.6182,0.0306</t>
+  </si>
+  <si>
+    <t>0.7409,0.1029,0.1943,0.0548</t>
+  </si>
+  <si>
+    <t>0.2134,0.0134,0.8339,0.0017</t>
+  </si>
+  <si>
+    <t>0.9858,0.0146,0.0032,0.0006</t>
+  </si>
+  <si>
+    <t>0.6715,0.5234,0.0035,0.0006</t>
+  </si>
+  <si>
+    <t>0.9792,0.0239,0.0033,0.0015</t>
+  </si>
+  <si>
+    <t>0.9948,0.0057,0.0007,0.0003</t>
+  </si>
+  <si>
+    <t>0.9738,0.0427,0.0022,0.0012</t>
+  </si>
+  <si>
+    <t>0.9328,0.0101,0.0609,0.0047</t>
+  </si>
+  <si>
+    <t>0.9615,0.0019,0.0488,0.0027</t>
+  </si>
+  <si>
+    <t>0.7748,0.0492,0.0973,0.1086</t>
+  </si>
+  <si>
+    <t>0.7716,0.0209,0.3100,0.0190</t>
+  </si>
+  <si>
+    <t>0.5047,0.0170,0.4969,0.0249</t>
+  </si>
+  <si>
+    <t>0.0035,0.0029,0.9860,0.0066</t>
+  </si>
+  <si>
+    <t>0.0230,0.2088,0.9042,0.0146</t>
+  </si>
+  <si>
+    <t>0.0574,0.1500,0.8841,0.0360</t>
+  </si>
+  <si>
+    <t>0.3849,0.0047,0.7710,0.0017</t>
+  </si>
+  <si>
+    <t>0.0090,0.0776,0.9326,0.0192</t>
+  </si>
+  <si>
+    <t>0.9882,0.0012,0.0004,0.0086</t>
+  </si>
+  <si>
+    <t>0.9965,0.0014,0.0005,0.0007</t>
+  </si>
+  <si>
+    <t>0.9905,0.0056,0.0011,0.0018</t>
+  </si>
+  <si>
+    <t>0.9918,0.0098,0.0014,0.0004</t>
+  </si>
+  <si>
+    <t>0.9839,0.0151,0.0015,0.0021</t>
+  </si>
+  <si>
+    <t>0.9952,0.0015,0.0005,0.0017</t>
+  </si>
+  <si>
+    <t>0.9932,0.0027,0.0003,0.0018</t>
+  </si>
+  <si>
+    <t>0.9930,0.0016,0.0008,0.0028</t>
+  </si>
+  <si>
+    <t>0.0533,0.0770,0.9121,0.0293</t>
+  </si>
+  <si>
+    <t>0.1299,0.2591,0.7252,0.0144</t>
+  </si>
+  <si>
+    <t>0.9750,0.0148,0.0065,0.0036</t>
+  </si>
+  <si>
+    <t>0.0008,0.0021,0.9951,0.0018</t>
+  </si>
+  <si>
+    <t>0.0017,0.0103,0.9864,0.0115</t>
+  </si>
+  <si>
+    <t>0.0029,0.0608,0.9876,0.0012</t>
+  </si>
+  <si>
+    <t>0.0031,0.0017,0.9961,0.0007</t>
+  </si>
+  <si>
+    <t>0.2817,0.0270,0.7079,0.0055</t>
+  </si>
+  <si>
+    <t>0.0024,0.0019,0.9961,0.0008</t>
+  </si>
+  <si>
+    <t>0.0059,0.1194,0.9465,0.0152</t>
+  </si>
+  <si>
+    <t>0.4116,0.0252,0.6301,0.0110</t>
+  </si>
+  <si>
+    <t>0.8588,0.0009,0.1398,0.0103</t>
+  </si>
+  <si>
+    <t>0.8946,0.0018,0.1791,0.0041</t>
+  </si>
+  <si>
+    <t>0.9598,0.0019,0.0240,0.0085</t>
+  </si>
+  <si>
+    <t>0.9956,0.0009,0.0003,0.0014</t>
+  </si>
+  <si>
+    <t>0.9920,0.0037,0.0013,0.0023</t>
+  </si>
+  <si>
+    <t>0.9968,0.0011,0.0004,0.0008</t>
+  </si>
+  <si>
+    <t>0.9983,0.0009,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9952,0.0003,0.0002,0.0039</t>
+  </si>
+  <si>
+    <t>0.9952,0.0011,0.0002,0.0011</t>
+  </si>
+  <si>
+    <t>0.9943,0.0012,0.0003,0.0022</t>
+  </si>
+  <si>
+    <t>0.9981,0.0004,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.0072,0.0326,0.9663,0.0014</t>
+  </si>
+  <si>
+    <t>0.0032,0.0618,0.9728,0.0035</t>
+  </si>
+  <si>
+    <t>0.0037,0.0151,0.9885,0.0027</t>
+  </si>
+  <si>
+    <t>0.0148,0.0108,0.9708,0.0019</t>
+  </si>
+  <si>
+    <t>0.0169,0.0024,0.9883,0.0007</t>
+  </si>
+  <si>
+    <t>0.4483,0.0601,0.3937,0.1671</t>
+  </si>
+  <si>
+    <t>0.0086,0.0273,0.9814,0.0014</t>
+  </si>
+  <si>
+    <t>0.0696,0.0249,0.8748,0.0527</t>
+  </si>
+  <si>
+    <t>0.8232,0.0003,0.0011,0.2854</t>
+  </si>
+  <si>
+    <t>0.0892,0.0028,0.0014,0.9649</t>
+  </si>
+  <si>
+    <t>0.1366,0.0028,0.0030,0.9399</t>
+  </si>
+  <si>
+    <t>0.0007,0.0001,0.0016,0.9991</t>
+  </si>
+  <si>
+    <t>0.0064,0.0002,0.0009,0.9967</t>
+  </si>
+  <si>
+    <t>0.1927,0.0196,0.0195,0.8600</t>
   </si>
 </sst>
 </file>
@@ -1967,7 +1967,7 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
         <v>265</v>
@@ -1995,7 +1995,7 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
         <v>267</v>
@@ -2135,7 +2135,7 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
         <v>277</v>
@@ -2149,7 +2149,7 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
         <v>278</v>
@@ -2163,7 +2163,7 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
         <v>279</v>
@@ -2191,7 +2191,7 @@
         <v>262</v>
       </c>
       <c r="C19" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D19" t="s">
         <v>281</v>
@@ -2219,7 +2219,7 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
         <v>283</v>
@@ -2233,7 +2233,7 @@
         <v>262</v>
       </c>
       <c r="C22" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D22" t="s">
         <v>284</v>
@@ -2275,7 +2275,7 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
         <v>287</v>
@@ -2289,7 +2289,7 @@
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s">
         <v>288</v>
@@ -2303,7 +2303,7 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
         <v>289</v>
@@ -2317,7 +2317,7 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D28" t="s">
         <v>290</v>
@@ -2331,7 +2331,7 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
         <v>291</v>
@@ -2345,7 +2345,7 @@
         <v>261</v>
       </c>
       <c r="C30" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D30" t="s">
         <v>292</v>
@@ -2359,7 +2359,7 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
         <v>293</v>
@@ -2387,7 +2387,7 @@
         <v>261</v>
       </c>
       <c r="C33" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D33" t="s">
         <v>295</v>
@@ -2401,7 +2401,7 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
         <v>296</v>
@@ -2443,7 +2443,7 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D37" t="s">
         <v>299</v>
@@ -2457,7 +2457,7 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
         <v>300</v>
@@ -2471,7 +2471,7 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
         <v>301</v>
@@ -2485,7 +2485,7 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D40" t="s">
         <v>302</v>
@@ -2499,7 +2499,7 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
         <v>303</v>
@@ -2527,7 +2527,7 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
         <v>305</v>
@@ -2555,7 +2555,7 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D45" t="s">
         <v>307</v>
@@ -2583,7 +2583,7 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D47" t="s">
         <v>309</v>
@@ -2597,7 +2597,7 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D48" t="s">
         <v>310</v>
@@ -2611,7 +2611,7 @@
         <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D49" t="s">
         <v>311</v>
@@ -2625,7 +2625,7 @@
         <v>261</v>
       </c>
       <c r="C50" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D50" t="s">
         <v>312</v>
@@ -2639,7 +2639,7 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D51" t="s">
         <v>313</v>
@@ -2653,7 +2653,7 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D52" t="s">
         <v>314</v>
@@ -2667,7 +2667,7 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D53" t="s">
         <v>315</v>
@@ -2681,7 +2681,7 @@
         <v>261</v>
       </c>
       <c r="C54" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D54" t="s">
         <v>316</v>
@@ -2695,7 +2695,7 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D55" t="s">
         <v>317</v>
@@ -2751,7 +2751,7 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D59" t="s">
         <v>321</v>
@@ -2821,7 +2821,7 @@
         <v>261</v>
       </c>
       <c r="C64" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D64" t="s">
         <v>326</v>
@@ -2835,7 +2835,7 @@
         <v>261</v>
       </c>
       <c r="C65" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D65" t="s">
         <v>327</v>
@@ -2863,7 +2863,7 @@
         <v>261</v>
       </c>
       <c r="C67" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D67" t="s">
         <v>329</v>
@@ -2877,7 +2877,7 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D68" t="s">
         <v>330</v>
@@ -2919,7 +2919,7 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
         <v>333</v>
@@ -2933,7 +2933,7 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D72" t="s">
         <v>334</v>
@@ -2947,7 +2947,7 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
         <v>335</v>
@@ -2961,7 +2961,7 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
         <v>336</v>
@@ -2989,7 +2989,7 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D76" t="s">
         <v>338</v>
@@ -3003,7 +3003,7 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
         <v>339</v>
@@ -3017,7 +3017,7 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
         <v>340</v>
@@ -3031,7 +3031,7 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D79" t="s">
         <v>341</v>
@@ -3045,7 +3045,7 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
         <v>342</v>
@@ -3059,7 +3059,7 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
         <v>343</v>
@@ -3073,7 +3073,7 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
         <v>344</v>
@@ -3101,7 +3101,7 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D84" t="s">
         <v>346</v>
@@ -3115,7 +3115,7 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
         <v>347</v>
@@ -3129,7 +3129,7 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
         <v>348</v>
@@ -3143,7 +3143,7 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
         <v>349</v>
@@ -3409,7 +3409,7 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D106" t="s">
         <v>368</v>
@@ -3437,7 +3437,7 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D108" t="s">
         <v>370</v>
@@ -3479,7 +3479,7 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D111" t="s">
         <v>373</v>
@@ -3563,7 +3563,7 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
         <v>379</v>
@@ -3591,7 +3591,7 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
         <v>381</v>
@@ -3605,7 +3605,7 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
         <v>382</v>
@@ -3619,7 +3619,7 @@
         <v>262</v>
       </c>
       <c r="C121" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D121" t="s">
         <v>383</v>
@@ -3633,7 +3633,7 @@
         <v>262</v>
       </c>
       <c r="C122" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D122" t="s">
         <v>384</v>
@@ -3647,7 +3647,7 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
         <v>385</v>
@@ -3661,7 +3661,7 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D124" t="s">
         <v>386</v>
@@ -3675,7 +3675,7 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D125" t="s">
         <v>387</v>
@@ -3689,7 +3689,7 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D126" t="s">
         <v>388</v>
@@ -3829,7 +3829,7 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D136" t="s">
         <v>398</v>
@@ -3843,7 +3843,7 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D137" t="s">
         <v>399</v>
@@ -3857,7 +3857,7 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D138" t="s">
         <v>400</v>
@@ -3871,7 +3871,7 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D139" t="s">
         <v>401</v>
@@ -3913,7 +3913,7 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
         <v>404</v>
@@ -3941,7 +3941,7 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
         <v>406</v>
@@ -3955,7 +3955,7 @@
         <v>260</v>
       </c>
       <c r="C145" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D145" t="s">
         <v>407</v>
@@ -3969,7 +3969,7 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
         <v>408</v>
@@ -3983,7 +3983,7 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
         <v>409</v>
@@ -3997,7 +3997,7 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D148" t="s">
         <v>410</v>
@@ -4053,7 +4053,7 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
         <v>414</v>
@@ -4389,7 +4389,7 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
         <v>438</v>
@@ -4445,7 +4445,7 @@
         <v>259</v>
       </c>
       <c r="C180" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D180" t="s">
         <v>442</v>
@@ -4487,7 +4487,7 @@
         <v>261</v>
       </c>
       <c r="C183" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D183" t="s">
         <v>445</v>
@@ -4501,7 +4501,7 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D184" t="s">
         <v>446</v>
@@ -4515,7 +4515,7 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D185" t="s">
         <v>447</v>
@@ -4543,7 +4543,7 @@
         <v>261</v>
       </c>
       <c r="C187" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D187" t="s">
         <v>449</v>
@@ -4557,7 +4557,7 @@
         <v>261</v>
       </c>
       <c r="C188" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D188" t="s">
         <v>450</v>
@@ -4571,7 +4571,7 @@
         <v>261</v>
       </c>
       <c r="C189" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D189" t="s">
         <v>451</v>
@@ -4585,7 +4585,7 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
         <v>452</v>
@@ -4599,7 +4599,7 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
         <v>453</v>
@@ -4613,7 +4613,7 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
         <v>454</v>
@@ -4627,7 +4627,7 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
         <v>455</v>
@@ -4641,7 +4641,7 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
         <v>456</v>
@@ -4655,7 +4655,7 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D195" t="s">
         <v>457</v>
@@ -4683,7 +4683,7 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
         <v>459</v>
@@ -4711,7 +4711,7 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D199" t="s">
         <v>461</v>
@@ -4837,7 +4837,7 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D208" t="s">
         <v>470</v>
@@ -4851,7 +4851,7 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
         <v>471</v>
@@ -4865,7 +4865,7 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
         <v>472</v>
@@ -4879,7 +4879,7 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D211" t="s">
         <v>473</v>
@@ -4893,7 +4893,7 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
         <v>474</v>
@@ -5019,7 +5019,7 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
         <v>483</v>
@@ -5033,7 +5033,7 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
         <v>484</v>
@@ -5061,7 +5061,7 @@
         <v>261</v>
       </c>
       <c r="C224" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D224" t="s">
         <v>486</v>
@@ -5075,7 +5075,7 @@
         <v>261</v>
       </c>
       <c r="C225" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D225" t="s">
         <v>487</v>
@@ -5089,7 +5089,7 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
         <v>488</v>
@@ -5103,7 +5103,7 @@
         <v>261</v>
       </c>
       <c r="C227" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D227" t="s">
         <v>489</v>
@@ -5117,7 +5117,7 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
         <v>490</v>
@@ -5131,7 +5131,7 @@
         <v>261</v>
       </c>
       <c r="C229" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D229" t="s">
         <v>491</v>
@@ -5145,7 +5145,7 @@
         <v>261</v>
       </c>
       <c r="C230" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D230" t="s">
         <v>492</v>
@@ -5159,7 +5159,7 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
         <v>493</v>
@@ -5327,7 +5327,7 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
         <v>505</v>
@@ -5341,7 +5341,7 @@
         <v>261</v>
       </c>
       <c r="C244" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D244" t="s">
         <v>506</v>
@@ -5369,7 +5369,7 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
         <v>508</v>
@@ -5383,7 +5383,7 @@
         <v>261</v>
       </c>
       <c r="C247" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D247" t="s">
         <v>509</v>
@@ -5411,7 +5411,7 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
         <v>511</v>
@@ -5425,7 +5425,7 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
         <v>512</v>
@@ -5453,7 +5453,7 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
         <v>514</v>
@@ -5467,7 +5467,7 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
         <v>515</v>
@@ -5481,7 +5481,7 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
         <v>516</v>
@@ -5495,7 +5495,7 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D255" t="s">
         <v>517</v>
@@ -5509,7 +5509,7 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D256" t="s">
         <v>518</v>
